--- a/reports/Lawrence_Client1_Kenya_Dashboard_Output.xlsx
+++ b/reports/Lawrence_Client1_Kenya_Dashboard_Output.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>14546263.5</v>
+        <v>14448633.45</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>528000</v>
+        <v>507497.1</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.62979812650857</v>
+        <v>3.512422830548033</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>564375</v>
+        <v>583841.5</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3.879862344030823</v>
+        <v>4.040807748500257</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>649687.5</v>
+        <v>654637.5</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.466353163477343</v>
+        <v>4.530791803013039</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>0</v>
+        <v>145464</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0</v>
+        <v>1.00676649112446</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1253175</v>
+        <v>1256346</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8.615098990885185</v>
+        <v>8.695258304860658</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>913135.5</v>
+        <v>871911</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6.277457437781186</v>
+        <v>6.034556852848945</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>416905.0000000001</v>
+        <v>437430</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>2.866062477144045</v>
+        <v>3.027483543781091</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>378750</v>
+        <v>354922.4</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.603761440180153</v>
+        <v>2.456442688702854</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>418327</v>
+        <v>407288.7</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2.875838183462028</v>
+        <v>2.81887350391604</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>752584.5</v>
+        <v>797568</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5.173730697233692</v>
+        <v>5.520023763908275</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>776325</v>
+        <v>800085.25</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5.336937557882132</v>
+        <v>5.537445826753949</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>1306050</v>
+        <v>1358292</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>8.97859439986083</v>
+        <v>9.400833682302322</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1019,10 +1019,10 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>538949</v>
+        <v>573350</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3.705068315309976</v>
+        <v>3.968195345145253</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>3050000</v>
+        <v>3700000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>20.96758387471807</v>
+        <v>25.6079581007019</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>20.62385299152597</v>
+        <v>13.84213951389292</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>11.97601363401674</v>
+        <v>13.09078887318579</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>20.62385299152597</v>
+        <v>13.84213951389292</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>12.68366271517081</v>
+        <v>13.36902902744758</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>13.38650643857785</v>
+        <v>13.87634309457826</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>20.96758387471807</v>
+        <v>25.6079581007019</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>11.74728135510538</v>
+        <v>11.51848308533289</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>8.615098990885185</v>
+        <v>8.695258304860658</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1453,25 +1453,25 @@
         <v>5</v>
       </c>
       <c r="D2" s="19" t="n">
-        <v>16500</v>
+        <v>15909</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>30.8417949557812</v>
+        <v>27.38706471631819</v>
       </c>
       <c r="F2" s="20" t="n">
         <v>32.1</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="H2" s="18" t="n">
-        <v>529650</v>
+        <v>510678.9</v>
       </c>
       <c r="I2" s="20" t="n">
-        <v>528000</v>
+        <v>507497.1</v>
       </c>
       <c r="J2" s="20" t="n">
-        <v>33000</v>
+        <v>31818</v>
       </c>
       <c r="K2" s="18" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L2" s="18" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="M2" s="18" t="inlineStr">
         <is>
@@ -1488,14 +1488,14 @@
       </c>
       <c r="N2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O2" s="21" t="n">
-        <v>3.62979812650857</v>
+        <v>3.512422830548033</v>
       </c>
       <c r="P2" s="21" t="n">
-        <v>-0.3115264797507832</v>
+        <v>-0.6230529595015665</v>
       </c>
     </row>
     <row r="3">
@@ -1513,25 +1513,25 @@
         <v>5</v>
       </c>
       <c r="D3" s="24" t="n">
-        <v>7500</v>
+        <v>7733</v>
       </c>
       <c r="E3" s="23" t="n">
-        <v>32.42712086472322</v>
+        <v>30.79229380782754</v>
       </c>
       <c r="F3" s="25" t="n">
         <v>74.25</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="H3" s="23" t="n">
-        <v>556875</v>
+        <v>574175.25</v>
       </c>
       <c r="I3" s="25" t="n">
-        <v>564375</v>
+        <v>583841.5</v>
       </c>
       <c r="J3" s="25" t="n">
-        <v>15000</v>
+        <v>15466</v>
       </c>
       <c r="K3" s="23" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="L3" s="23" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="M3" s="23" t="inlineStr">
         <is>
@@ -1548,14 +1548,14 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O3" s="26" t="n">
-        <v>3.879862344030823</v>
+        <v>4.040807748500257</v>
       </c>
       <c r="P3" s="26" t="n">
-        <v>1.346801346801347</v>
+        <v>1.683501683501683</v>
       </c>
     </row>
     <row r="4">
@@ -1573,10 +1573,10 @@
         <v>5</v>
       </c>
       <c r="D4" s="19" t="n">
-        <v>9450</v>
+        <v>9522</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>36.73108417949557</v>
+        <v>34.08607701976954</v>
       </c>
       <c r="F4" s="20" t="n">
         <v>66.75</v>
@@ -1585,13 +1585,13 @@
         <v>68.75</v>
       </c>
       <c r="H4" s="18" t="n">
-        <v>630787.5</v>
+        <v>635593.5</v>
       </c>
       <c r="I4" s="20" t="n">
-        <v>649687.5</v>
+        <v>654637.5</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>18900</v>
+        <v>19044</v>
       </c>
       <c r="K4" s="18" t="inlineStr">
         <is>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="N4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O4" s="21" t="n">
-        <v>4.466353163477343</v>
+        <v>4.530791803013039</v>
       </c>
       <c r="P4" s="21" t="n">
         <v>2.99625468164794</v>
@@ -1631,10 +1631,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>0</v>
+        <v>1653</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>0</v>
+        <v>7.734564456084741</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>87.25</v>
@@ -1643,13 +1643,13 @@
         <v>88</v>
       </c>
       <c r="H5" s="23" t="n">
-        <v>0</v>
+        <v>144224.25</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>0</v>
+        <v>145464</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>0</v>
+        <v>3306</v>
       </c>
       <c r="K5" s="23" t="inlineStr">
         <is>
@@ -1666,11 +1666,11 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O5" s="26" t="n">
-        <v>0</v>
+        <v>1.00676649112446</v>
       </c>
       <c r="P5" s="26" t="n">
         <v>0.8595988538681949</v>
@@ -1691,7 +1691,7 @@
         <v>10</v>
       </c>
       <c r="D6" s="19" t="n">
-        <v>40425</v>
+        <v>39884</v>
       </c>
       <c r="E6" s="18" t="n">
         <v>100</v>
@@ -1700,16 +1700,16 @@
         <v>30.55</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>1234983.75</v>
+        <v>1218456.2</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>1253175</v>
+        <v>1256346</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>80850</v>
+        <v>79768</v>
       </c>
       <c r="K6" s="18" t="inlineStr">
         <is>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="L6" s="18" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
@@ -1726,14 +1726,14 @@
       </c>
       <c r="N6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>8.615098990885185</v>
+        <v>8.695258304860658</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>1.472995090016364</v>
+        <v>3.10965630114566</v>
       </c>
     </row>
     <row r="7">
@@ -1751,25 +1751,25 @@
         <v>3.33</v>
       </c>
       <c r="D7" s="24" t="n">
-        <v>2358</v>
+        <v>2253</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>51.28750438029412</v>
+        <v>50.02650032779237</v>
       </c>
       <c r="F7" s="25" t="n">
         <v>360</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="H7" s="23" t="n">
-        <v>848880</v>
+        <v>811080</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>913135.5</v>
+        <v>871911</v>
       </c>
       <c r="J7" s="25" t="n">
-        <v>4716</v>
+        <v>4506</v>
       </c>
       <c r="K7" s="23" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="L7" s="23" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="M7" s="23" t="inlineStr">
         <is>
@@ -1786,14 +1786,14 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O7" s="26" t="n">
-        <v>6.277457437781186</v>
+        <v>6.034556852848945</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>7.569444444444444</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8">
@@ -1811,25 +1811,25 @@
         <v>3.33</v>
       </c>
       <c r="D8" s="19" t="n">
-        <v>99500</v>
+        <v>104150</v>
       </c>
       <c r="E8" s="18" t="n">
-        <v>25.18850369153063</v>
+        <v>26.91595087820539</v>
       </c>
       <c r="F8" s="20" t="n">
         <v>4.19</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>416905.0000000001</v>
+        <v>436388.5000000001</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>416905.0000000001</v>
+        <v>437430</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>198999.9999999999</v>
+        <v>208299.9999999999</v>
       </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="L8" s="18" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="M8" s="18" t="inlineStr">
         <is>
@@ -1846,14 +1846,14 @@
       </c>
       <c r="N8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>2.866062477144045</v>
+        <v>3.027483543781091</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>0</v>
+        <v>0.2386634844868684</v>
       </c>
     </row>
     <row r="9">
@@ -1871,25 +1871,25 @@
         <v>3.34</v>
       </c>
       <c r="D9" s="24" t="n">
-        <v>30300</v>
+        <v>29092</v>
       </c>
       <c r="E9" s="23" t="n">
-        <v>23.52399192817526</v>
+        <v>23.05754879400225</v>
       </c>
       <c r="F9" s="25" t="n">
         <v>12.85</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>389355</v>
+        <v>373832.2</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>378750</v>
+        <v>354922.4</v>
       </c>
       <c r="J9" s="25" t="n">
-        <v>60600</v>
+        <v>58184</v>
       </c>
       <c r="K9" s="23" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="L9" s="23" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
@@ -1906,14 +1906,14 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O9" s="26" t="n">
-        <v>2.603761440180153</v>
+        <v>2.456442688702854</v>
       </c>
       <c r="P9" s="26" t="n">
-        <v>-2.723735408560309</v>
+        <v>-5.058365758754866</v>
       </c>
     </row>
     <row r="10">
@@ -1931,10 +1931,10 @@
         <v>3.33</v>
       </c>
       <c r="D10" s="19" t="n">
-        <v>45970</v>
+        <v>44757</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>20.51039114590646</v>
+        <v>19.38233001962682</v>
       </c>
       <c r="F10" s="20" t="n">
         <v>9.18</v>
@@ -1943,13 +1943,13 @@
         <v>9.1</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>422004.6</v>
+        <v>410869.26</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>418327</v>
+        <v>407288.7</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>91940</v>
+        <v>89514</v>
       </c>
       <c r="K10" s="18" t="inlineStr">
         <is>
@@ -1966,11 +1966,11 @@
       </c>
       <c r="N10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>2.875838183462028</v>
+        <v>2.81887350391604</v>
       </c>
       <c r="P10" s="21" t="n">
         <v>-0.8714596949891076</v>
@@ -1991,25 +1991,25 @@
         <v>3.33</v>
       </c>
       <c r="D11" s="24" t="n">
-        <v>46890</v>
+        <v>49848</v>
       </c>
       <c r="E11" s="23" t="n">
-        <v>34.98205919263523</v>
+        <v>36.09594798516148</v>
       </c>
       <c r="F11" s="25" t="n">
         <v>15.35</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>719761.5</v>
+        <v>765166.7999999999</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>752584.5</v>
+        <v>797568</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>93780.00000000012</v>
+        <v>99696.00000000012</v>
       </c>
       <c r="K11" s="23" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="L11" s="23" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="M11" s="23" t="inlineStr">
         <is>
@@ -2026,14 +2026,14 @@
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O11" s="26" t="n">
-        <v>5.173730697233692</v>
+        <v>5.520023763908275</v>
       </c>
       <c r="P11" s="26" t="n">
-        <v>4.560260586319225</v>
+        <v>4.23452768729642</v>
       </c>
     </row>
     <row r="12">
@@ -2051,10 +2051,10 @@
         <v>3.34</v>
       </c>
       <c r="D12" s="19" t="n">
-        <v>16500</v>
+        <v>17005</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>44.5075496614583</v>
+        <v>44.52172199521168</v>
       </c>
       <c r="F12" s="20" t="n">
         <v>55.5</v>
@@ -2063,13 +2063,13 @@
         <v>47.05</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>915750</v>
+        <v>943777.5</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>776325</v>
+        <v>800085.25</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>33000</v>
+        <v>34010</v>
       </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
@@ -2086,11 +2086,11 @@
       </c>
       <c r="N12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>5.336937557882132</v>
+        <v>5.537445826753949</v>
       </c>
       <c r="P12" s="21" t="n">
         <v>-15.22522522522523</v>
@@ -2111,10 +2111,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="24" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="23" t="n">
-        <v>70.79147141645278</v>
+        <v>70.32084038747288</v>
       </c>
       <c r="F13" s="25" t="n">
         <v>52240</v>
@@ -2123,13 +2123,13 @@
         <v>52242</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>1306000</v>
+        <v>1358240</v>
       </c>
       <c r="I13" s="25" t="n">
-        <v>1306050</v>
+        <v>1358292</v>
       </c>
       <c r="J13" s="25" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K13" s="23" t="inlineStr"/>
       <c r="L13" s="23" t="inlineStr"/>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr"/>
       <c r="O13" s="26" t="n">
-        <v>8.97859439986083</v>
+        <v>9.400833682302322</v>
       </c>
       <c r="P13" s="26" t="n">
         <v>0.003828483920367535</v>
@@ -2161,10 +2161,10 @@
         <v>5</v>
       </c>
       <c r="D14" s="19" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>29.20852858354722</v>
+        <v>29.67915961252712</v>
       </c>
       <c r="F14" s="20" t="n">
         <v>11465</v>
@@ -2173,13 +2173,13 @@
         <v>11467</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>538855</v>
+        <v>573250</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>538949</v>
+        <v>573350</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K14" s="18" t="inlineStr"/>
       <c r="L14" s="18" t="inlineStr"/>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N14" s="18" t="inlineStr"/>
       <c r="O14" s="21" t="n">
-        <v>3.705068315309976</v>
+        <v>3.968195345145253</v>
       </c>
       <c r="P14" s="21" t="n">
         <v>0.01744439598778892</v>
@@ -2211,7 +2211,7 @@
         <v>30</v>
       </c>
       <c r="D15" s="24" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E15" s="23" t="n">
         <v>100</v>
@@ -2223,10 +2223,10 @@
         <v>50000</v>
       </c>
       <c r="H15" s="23" t="n">
-        <v>3050000</v>
+        <v>3700000</v>
       </c>
       <c r="I15" s="25" t="n">
-        <v>3050000</v>
+        <v>3700000</v>
       </c>
       <c r="J15" s="25" t="n">
         <v>0</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr"/>
       <c r="O15" s="26" t="n">
-        <v>20.96758387471807</v>
+        <v>25.6079581007019</v>
       </c>
       <c r="P15" s="26" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E16" s="18" t="n">
         <v>100</v>
@@ -2273,10 +2273,10 @@
         <v>1000000</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="I16" s="20" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
       <c r="J16" s="20" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="N16" s="18" t="inlineStr"/>
       <c r="O16" s="21" t="n">
-        <v>20.62385299152597</v>
+        <v>13.84213951389292</v>
       </c>
       <c r="P16" s="21" t="n">
         <v>0</v>
@@ -2370,14 +2370,14 @@
       </c>
       <c r="C2" s="20" t="inlineStr"/>
       <c r="D2" s="20" t="n">
-        <v>16500</v>
+        <v>15909</v>
       </c>
       <c r="E2" s="20" t="inlineStr"/>
       <c r="F2" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>528000</v>
+        <v>507497.1</v>
       </c>
       <c r="H2" s="18" t="n">
         <v>0</v>
@@ -2392,14 +2392,14 @@
       </c>
       <c r="C3" s="25" t="inlineStr"/>
       <c r="D3" s="25" t="n">
-        <v>7500</v>
+        <v>7733</v>
       </c>
       <c r="E3" s="25" t="inlineStr"/>
       <c r="F3" s="25" t="n">
         <v>0</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>564375</v>
+        <v>583841.5</v>
       </c>
       <c r="H3" s="23" t="n">
         <v>0</v>
@@ -2414,14 +2414,14 @@
       </c>
       <c r="C4" s="20" t="inlineStr"/>
       <c r="D4" s="20" t="n">
-        <v>9450</v>
+        <v>9522</v>
       </c>
       <c r="E4" s="20" t="inlineStr"/>
       <c r="F4" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="20" t="n">
-        <v>649687.5</v>
+        <v>654637.5</v>
       </c>
       <c r="H4" s="18" t="n">
         <v>0</v>
@@ -2436,14 +2436,14 @@
       </c>
       <c r="C5" s="25" t="inlineStr"/>
       <c r="D5" s="25" t="n">
-        <v>0</v>
+        <v>1653</v>
       </c>
       <c r="E5" s="25" t="inlineStr"/>
       <c r="F5" s="25" t="n">
         <v>0</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0</v>
+        <v>145464</v>
       </c>
       <c r="H5" s="23" t="n">
         <v>0</v>
@@ -2458,14 +2458,14 @@
       </c>
       <c r="C6" s="20" t="inlineStr"/>
       <c r="D6" s="20" t="n">
-        <v>40425</v>
+        <v>39884</v>
       </c>
       <c r="E6" s="20" t="inlineStr"/>
       <c r="F6" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>1253175</v>
+        <v>1256346</v>
       </c>
       <c r="H6" s="18" t="n">
         <v>0</v>
@@ -2480,14 +2480,14 @@
       </c>
       <c r="C7" s="25" t="inlineStr"/>
       <c r="D7" s="25" t="n">
-        <v>2358</v>
+        <v>2253</v>
       </c>
       <c r="E7" s="25" t="inlineStr"/>
       <c r="F7" s="25" t="n">
         <v>0</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>913135.5</v>
+        <v>871911</v>
       </c>
       <c r="H7" s="23" t="n">
         <v>0</v>
@@ -2502,14 +2502,14 @@
       </c>
       <c r="C8" s="20" t="inlineStr"/>
       <c r="D8" s="20" t="n">
-        <v>99500</v>
+        <v>104150</v>
       </c>
       <c r="E8" s="20" t="inlineStr"/>
       <c r="F8" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>416905.0000000001</v>
+        <v>437430</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0</v>
@@ -2524,14 +2524,14 @@
       </c>
       <c r="C9" s="25" t="inlineStr"/>
       <c r="D9" s="25" t="n">
-        <v>30300</v>
+        <v>29092</v>
       </c>
       <c r="E9" s="25" t="inlineStr"/>
       <c r="F9" s="25" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>378750</v>
+        <v>354922.4</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>0</v>
@@ -2546,14 +2546,14 @@
       </c>
       <c r="C10" s="20" t="inlineStr"/>
       <c r="D10" s="20" t="n">
-        <v>45970</v>
+        <v>44757</v>
       </c>
       <c r="E10" s="20" t="inlineStr"/>
       <c r="F10" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>418327</v>
+        <v>407288.7</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C11" s="25" t="inlineStr"/>
       <c r="D11" s="25" t="n">
-        <v>46890</v>
+        <v>49848</v>
       </c>
       <c r="E11" s="25" t="inlineStr"/>
       <c r="F11" s="25" t="n">
@@ -2588,14 +2588,14 @@
       </c>
       <c r="C12" s="20" t="inlineStr"/>
       <c r="D12" s="20" t="n">
-        <v>16500</v>
+        <v>17005</v>
       </c>
       <c r="E12" s="20" t="inlineStr"/>
       <c r="F12" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>776325</v>
+        <v>800085.25</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>0</v>
@@ -2610,14 +2610,14 @@
       </c>
       <c r="C13" s="25" t="inlineStr"/>
       <c r="D13" s="25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="25" t="inlineStr"/>
       <c r="F13" s="25" t="n">
         <v>0</v>
       </c>
       <c r="G13" s="25" t="n">
-        <v>1306050</v>
+        <v>1358292</v>
       </c>
       <c r="H13" s="23" t="n">
         <v>0</v>
@@ -2632,14 +2632,14 @@
       </c>
       <c r="C14" s="20" t="inlineStr"/>
       <c r="D14" s="20" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E14" s="20" t="inlineStr"/>
       <c r="F14" s="20" t="n">
         <v>0</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>538949</v>
+        <v>573350</v>
       </c>
       <c r="H14" s="18" t="n">
         <v>0</v>
@@ -2760,20 +2760,20 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="B2" s="20" t="n">
-        <v>14546263.5</v>
+        <v>14448633.45</v>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
-          <t>Treasury Bonds (KES 3,050,000)</t>
+          <t>Treasury Bonds (KES 3,700,000)</t>
         </is>
       </c>
       <c r="D2" s="20" t="inlineStr">
         <is>
-          <t>Fixed Income (KES 3,050,000)</t>
+          <t>Fixed Income (KES 3,700,000)</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="C2" s="20" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" s="20" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="C8" s="20" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:29</t>
+          <t>2026-06-03 10:17:26</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3393,7 +3393,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
@@ -3407,7 +3407,7 @@
         </is>
       </c>
       <c r="D2" s="20" t="n">
-        <v>16500</v>
+        <v>15909</v>
       </c>
       <c r="E2" s="20" t="n">
         <v>32.1</v>
@@ -3425,22 +3425,22 @@
         <v>0</v>
       </c>
       <c r="J2" s="20" t="n">
-        <v>-1650</v>
+        <v>-3181.800000000047</v>
       </c>
       <c r="K2" s="20" t="n">
-        <v>529650</v>
+        <v>510678.9</v>
       </c>
       <c r="L2" s="20" t="n">
         <v>32.1</v>
       </c>
       <c r="M2" s="20" t="n">
-        <v>16500</v>
+        <v>15909</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B3" s="22" t="inlineStr">
@@ -3454,7 +3454,7 @@
         </is>
       </c>
       <c r="D3" s="25" t="n">
-        <v>7500</v>
+        <v>7733</v>
       </c>
       <c r="E3" s="25" t="n">
         <v>74.25</v>
@@ -3472,22 +3472,22 @@
         <v>0</v>
       </c>
       <c r="J3" s="25" t="n">
-        <v>7500</v>
+        <v>9666.25</v>
       </c>
       <c r="K3" s="25" t="n">
-        <v>556875</v>
+        <v>574175.25</v>
       </c>
       <c r="L3" s="25" t="n">
         <v>74.25</v>
       </c>
       <c r="M3" s="25" t="n">
-        <v>7500</v>
+        <v>7733</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -3501,7 +3501,7 @@
         </is>
       </c>
       <c r="D4" s="20" t="n">
-        <v>9450</v>
+        <v>9522</v>
       </c>
       <c r="E4" s="20" t="n">
         <v>66.75</v>
@@ -3519,27 +3519,27 @@
         <v>0</v>
       </c>
       <c r="J4" s="20" t="n">
-        <v>18900</v>
+        <v>19044</v>
       </c>
       <c r="K4" s="20" t="n">
-        <v>630787.5</v>
+        <v>635593.5</v>
       </c>
       <c r="L4" s="20" t="n">
         <v>66.75</v>
       </c>
       <c r="M4" s="20" t="n">
-        <v>9450</v>
+        <v>9522</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>Safaricom</t>
+          <t>NCBA</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
@@ -3548,10 +3548,10 @@
         </is>
       </c>
       <c r="D5" s="25" t="n">
-        <v>40425</v>
+        <v>1653</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>30.55</v>
+        <v>87.25</v>
       </c>
       <c r="F5" s="22" t="inlineStr"/>
       <c r="G5" s="25" t="n">
@@ -3566,27 +3566,27 @@
         <v>0</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>18191.25</v>
+        <v>1239.75</v>
       </c>
       <c r="K5" s="25" t="n">
-        <v>1234983.75</v>
+        <v>144224.25</v>
       </c>
       <c r="L5" s="25" t="n">
-        <v>30.55</v>
+        <v>87.25</v>
       </c>
       <c r="M5" s="25" t="n">
-        <v>40425</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Jubilee</t>
+          <t>Safaricom</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="D6" s="20" t="n">
-        <v>2358</v>
+        <v>39884</v>
       </c>
       <c r="E6" s="20" t="n">
-        <v>360</v>
+        <v>30.55</v>
       </c>
       <c r="F6" s="17" t="inlineStr"/>
       <c r="G6" s="20" t="n">
@@ -3613,27 +3613,27 @@
         <v>0</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>64255.5</v>
+        <v>37889.80000000005</v>
       </c>
       <c r="K6" s="20" t="n">
-        <v>848880</v>
+        <v>1218456.2</v>
       </c>
       <c r="L6" s="20" t="n">
-        <v>360</v>
+        <v>30.55</v>
       </c>
       <c r="M6" s="20" t="n">
-        <v>2358</v>
+        <v>39884</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>CIC</t>
+          <t>Jubilee</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -3642,10 +3642,10 @@
         </is>
       </c>
       <c r="D7" s="25" t="n">
-        <v>99500</v>
+        <v>2253</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>4.19</v>
+        <v>360</v>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
       <c r="G7" s="25" t="n">
@@ -3660,27 +3660,27 @@
         <v>0</v>
       </c>
       <c r="J7" s="25" t="n">
-        <v>0</v>
+        <v>60831</v>
       </c>
       <c r="K7" s="25" t="n">
-        <v>416905.0000000001</v>
+        <v>811080</v>
       </c>
       <c r="L7" s="25" t="n">
-        <v>4.19</v>
+        <v>360</v>
       </c>
       <c r="M7" s="25" t="n">
-        <v>99500</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>Britam</t>
+          <t>CIC</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
@@ -3689,10 +3689,10 @@
         </is>
       </c>
       <c r="D8" s="20" t="n">
-        <v>30300</v>
+        <v>104150</v>
       </c>
       <c r="E8" s="20" t="n">
-        <v>12.85</v>
+        <v>4.19</v>
       </c>
       <c r="F8" s="17" t="inlineStr"/>
       <c r="G8" s="20" t="n">
@@ -3707,27 +3707,27 @@
         <v>0</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>-10605</v>
+        <v>1041.499999999942</v>
       </c>
       <c r="K8" s="20" t="n">
-        <v>389355</v>
+        <v>436388.5000000001</v>
       </c>
       <c r="L8" s="20" t="n">
-        <v>12.85</v>
+        <v>4.19</v>
       </c>
       <c r="M8" s="20" t="n">
-        <v>30300</v>
+        <v>104150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>KenGen</t>
+          <t>Britam</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -3736,10 +3736,10 @@
         </is>
       </c>
       <c r="D9" s="25" t="n">
-        <v>45970</v>
+        <v>29092</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>9.18</v>
+        <v>12.85</v>
       </c>
       <c r="F9" s="22" t="inlineStr"/>
       <c r="G9" s="25" t="n">
@@ -3754,27 +3754,27 @@
         <v>0</v>
       </c>
       <c r="J9" s="25" t="n">
-        <v>-3677.599999999977</v>
+        <v>-18909.80000000005</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>422004.6</v>
+        <v>373832.2</v>
       </c>
       <c r="L9" s="25" t="n">
-        <v>9.18</v>
+        <v>12.85</v>
       </c>
       <c r="M9" s="25" t="n">
-        <v>45970</v>
+        <v>29092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>Kenya Power</t>
+          <t>KenGen</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -3783,10 +3783,10 @@
         </is>
       </c>
       <c r="D10" s="20" t="n">
-        <v>46890</v>
+        <v>44757</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>15.35</v>
+        <v>9.18</v>
       </c>
       <c r="F10" s="17" t="inlineStr"/>
       <c r="G10" s="20" t="n">
@@ -3801,27 +3801,27 @@
         <v>0</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>32823</v>
+        <v>-3580.559999999998</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>719761.5</v>
+        <v>410869.26</v>
       </c>
       <c r="L10" s="20" t="n">
-        <v>15.35</v>
+        <v>9.18</v>
       </c>
       <c r="M10" s="20" t="n">
-        <v>46890</v>
+        <v>44757</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>Total Energies Marketing</t>
+          <t>Kenya Power</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -3830,10 +3830,10 @@
         </is>
       </c>
       <c r="D11" s="25" t="n">
-        <v>16500</v>
+        <v>49848</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>55.5</v>
+        <v>15.35</v>
       </c>
       <c r="F11" s="22" t="inlineStr"/>
       <c r="G11" s="25" t="n">
@@ -3848,27 +3848,27 @@
         <v>0</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>-139425</v>
+        <v>32401.20000000007</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>915750</v>
+        <v>765166.7999999999</v>
       </c>
       <c r="L11" s="25" t="n">
-        <v>55.5</v>
+        <v>15.35</v>
       </c>
       <c r="M11" s="25" t="n">
-        <v>16500</v>
+        <v>49848</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>VOO / IVV</t>
+          <t>Total Energies Marketing</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
@@ -3877,10 +3877,10 @@
         </is>
       </c>
       <c r="D12" s="20" t="n">
-        <v>25</v>
+        <v>17005</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>52240</v>
+        <v>55.5</v>
       </c>
       <c r="F12" s="17" t="inlineStr"/>
       <c r="G12" s="20" t="n">
@@ -3895,27 +3895,27 @@
         <v>0</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>50</v>
+        <v>-143692.25</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>1306000</v>
+        <v>943777.5</v>
       </c>
       <c r="L12" s="20" t="n">
-        <v>52240</v>
+        <v>55.5</v>
       </c>
       <c r="M12" s="20" t="n">
-        <v>25</v>
+        <v>17005</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>VOO / IVV</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="D13" s="25" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="E13" s="25" t="n">
-        <v>11465</v>
+        <v>52240</v>
       </c>
       <c r="F13" s="22" t="inlineStr"/>
       <c r="G13" s="25" t="n">
@@ -3942,27 +3942,27 @@
         <v>0</v>
       </c>
       <c r="J13" s="25" t="n">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>538855</v>
+        <v>1358240</v>
       </c>
       <c r="L13" s="25" t="n">
-        <v>11465</v>
+        <v>52240</v>
       </c>
       <c r="M13" s="25" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>Treasury Bonds</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="E14" s="20" t="n">
-        <v>50000</v>
+        <v>11465</v>
       </c>
       <c r="F14" s="17" t="inlineStr"/>
       <c r="G14" s="20" t="n">
@@ -3989,27 +3989,27 @@
         <v>0</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>3050000</v>
+        <v>573250</v>
       </c>
       <c r="L14" s="20" t="n">
-        <v>50000</v>
+        <v>11465</v>
       </c>
       <c r="M14" s="20" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>2026-06-02 21:41:46</t>
+          <t>2026-06-03 10:17:43</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>Money Market Fund</t>
+          <t>Treasury Bonds</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="D15" s="25" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>1000000</v>
+        <v>50000</v>
       </c>
       <c r="F15" s="22" t="inlineStr"/>
       <c r="G15" s="25" t="n">
@@ -4039,13 +4039,60 @@
         <v>0</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>3000000</v>
+        <v>3700000</v>
       </c>
       <c r="L15" s="25" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M15" s="25" t="n">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>2026-06-03 10:17:43</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Money Market Fund</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="20" t="n">
         <v>1000000</v>
       </c>
-      <c r="M15" s="25" t="n">
-        <v>3</v>
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L16" s="20" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M16" s="20" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4106,16 +4153,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16500</v>
+        <v>15909</v>
       </c>
       <c r="D2" t="n">
         <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="F2" t="n">
-        <v>528000</v>
+        <v>507497.1</v>
       </c>
     </row>
     <row r="3">
@@ -4130,16 +4177,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7500</v>
+        <v>7733</v>
       </c>
       <c r="D3" t="n">
         <v>74.25</v>
       </c>
       <c r="E3" t="n">
-        <v>75.25</v>
+        <v>75.5</v>
       </c>
       <c r="F3" t="n">
-        <v>564375</v>
+        <v>583841.5</v>
       </c>
     </row>
     <row r="4">
@@ -4154,7 +4201,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9450</v>
+        <v>9522</v>
       </c>
       <c r="D4" t="n">
         <v>66.75</v>
@@ -4163,7 +4210,7 @@
         <v>68.75</v>
       </c>
       <c r="F4" t="n">
-        <v>649687.5</v>
+        <v>654637.5</v>
       </c>
     </row>
     <row r="5">
@@ -4178,7 +4225,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>1653</v>
       </c>
       <c r="D5" t="n">
         <v>87.25</v>
@@ -4187,7 +4234,7 @@
         <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>145464</v>
       </c>
     </row>
     <row r="6">
@@ -4202,16 +4249,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>40425</v>
+        <v>39884</v>
       </c>
       <c r="D6" t="n">
         <v>30.55</v>
       </c>
       <c r="E6" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1253175</v>
+        <v>1256346</v>
       </c>
     </row>
     <row r="7">
@@ -4226,16 +4273,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2358</v>
+        <v>2253</v>
       </c>
       <c r="D7" t="n">
         <v>360</v>
       </c>
       <c r="E7" t="n">
-        <v>387.25</v>
+        <v>387</v>
       </c>
       <c r="F7" t="n">
-        <v>913135.5</v>
+        <v>871911</v>
       </c>
     </row>
     <row r="8">
@@ -4250,16 +4297,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>99500</v>
+        <v>104150</v>
       </c>
       <c r="D8" t="n">
         <v>4.19</v>
       </c>
       <c r="E8" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="F8" t="n">
-        <v>416905.0000000001</v>
+        <v>437430</v>
       </c>
     </row>
     <row r="9">
@@ -4274,16 +4321,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>30300</v>
+        <v>29092</v>
       </c>
       <c r="D9" t="n">
         <v>12.85</v>
       </c>
       <c r="E9" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="F9" t="n">
-        <v>378750</v>
+        <v>354922.4</v>
       </c>
     </row>
     <row r="10">
@@ -4298,7 +4345,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>45970</v>
+        <v>44757</v>
       </c>
       <c r="D10" t="n">
         <v>9.18</v>
@@ -4307,7 +4354,7 @@
         <v>9.1</v>
       </c>
       <c r="F10" t="n">
-        <v>418327</v>
+        <v>407288.7</v>
       </c>
     </row>
     <row r="11">
@@ -4322,16 +4369,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46890</v>
+        <v>49848</v>
       </c>
       <c r="D11" t="n">
         <v>15.35</v>
       </c>
       <c r="E11" t="n">
-        <v>16.05</v>
+        <v>16</v>
       </c>
       <c r="F11" t="n">
-        <v>752584.5</v>
+        <v>797568</v>
       </c>
     </row>
     <row r="12">
@@ -4346,7 +4393,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16500</v>
+        <v>17005</v>
       </c>
       <c r="D12" t="n">
         <v>55.5</v>
@@ -4355,7 +4402,7 @@
         <v>47.05</v>
       </c>
       <c r="F12" t="n">
-        <v>776325</v>
+        <v>800085.25</v>
       </c>
     </row>
     <row r="13">
@@ -4370,7 +4417,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D13" t="n">
         <v>52240</v>
@@ -4379,7 +4426,7 @@
         <v>52242</v>
       </c>
       <c r="F13" t="n">
-        <v>1306050</v>
+        <v>1358292</v>
       </c>
     </row>
     <row r="14">
@@ -4394,7 +4441,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
         <v>11465</v>
@@ -4403,7 +4450,7 @@
         <v>11467</v>
       </c>
       <c r="F14" t="n">
-        <v>538949</v>
+        <v>573350</v>
       </c>
     </row>
     <row r="15">
@@ -4418,7 +4465,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="D15" t="n">
         <v>50000</v>
@@ -4427,7 +4474,7 @@
         <v>50000</v>
       </c>
       <c r="F15" t="n">
-        <v>3050000</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="16">
@@ -4442,7 +4489,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>1000000</v>
@@ -4451,7 +4498,7 @@
         <v>1000000</v>
       </c>
       <c r="F16" t="n">
-        <v>3000000</v>
+        <v>2000000</v>
       </c>
     </row>
   </sheetData>

--- a/reports/Lawrence_Client1_Kenya_Dashboard_Output.xlsx
+++ b/reports/Lawrence_Client1_Kenya_Dashboard_Output.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>14448633.45</v>
+        <v>14428348.16</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -866,7 +866,7 @@
         <v>507497.1</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.512422830548033</v>
+        <v>3.517361061517384</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>583841.5</v>
+        <v>589641.25</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4.040807748500257</v>
+        <v>4.086685762370736</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -892,7 +892,7 @@
         <v>654637.5</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.530791803013039</v>
+        <v>4.537161792469527</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -905,7 +905,7 @@
         <v>145464</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1.00676649112446</v>
+        <v>1.008181937300853</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1256346</v>
+        <v>1246375</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8.695258304860658</v>
+        <v>8.638376245004611</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>871911</v>
+        <v>836989.5</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6.034556852848945</v>
+        <v>5.801007091861027</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>437430</v>
+        <v>435346.9999999999</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3.027483543781091</v>
+        <v>3.017303125571375</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>354922.4</v>
+        <v>362195.4</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.456442688702854</v>
+        <v>2.510303993107967</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>407288.7</v>
+        <v>406393.56</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2.81887350391604</v>
+        <v>2.816632614443371</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>797568</v>
+        <v>795075.6</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5.520023763908275</v>
+        <v>5.510510220457557</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>800085.25</v>
+        <v>817090.25</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5.537445826753949</v>
+        <v>5.663089363654501</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1009,7 +1009,7 @@
         <v>1358292</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9.400833682302322</v>
+        <v>9.414050624073656</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>573350</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3.968195345145253</v>
+        <v>3.973774361707668</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1035,7 +1035,7 @@
         <v>3700000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>25.6079581007019</v>
+        <v>25.64396117261423</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1048,7 +1048,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>13.84213951389292</v>
+        <v>13.86160063384553</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>13.09078887318579</v>
+        <v>13.1493905536585</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>13.84213951389292</v>
+        <v>13.86160063384553</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>13.36902902744758</v>
+        <v>13.38782498578132</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>13.87634309457826</v>
+        <v>13.99023219855543</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>25.6079581007019</v>
+        <v>25.64396117261423</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>11.51848308533289</v>
+        <v>11.32861421054037</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>8.695258304860658</v>
+        <v>8.638376245004611</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1488,11 +1488,11 @@
       </c>
       <c r="N2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O2" s="21" t="n">
-        <v>3.512422830548033</v>
+        <v>3.517361061517384</v>
       </c>
       <c r="P2" s="21" t="n">
         <v>-0.6230529595015665</v>
@@ -1522,13 +1522,13 @@
         <v>74.25</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>75.5</v>
+        <v>76.25</v>
       </c>
       <c r="H3" s="23" t="n">
         <v>574175.25</v>
       </c>
       <c r="I3" s="25" t="n">
-        <v>583841.5</v>
+        <v>589641.25</v>
       </c>
       <c r="J3" s="25" t="n">
         <v>15466</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="L3" s="23" t="n">
-        <v>75.5</v>
+        <v>76.25</v>
       </c>
       <c r="M3" s="23" t="inlineStr">
         <is>
@@ -1548,14 +1548,14 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O3" s="26" t="n">
-        <v>4.040807748500257</v>
+        <v>4.086685762370736</v>
       </c>
       <c r="P3" s="26" t="n">
-        <v>1.683501683501683</v>
+        <v>2.693602693602693</v>
       </c>
     </row>
     <row r="4">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="N4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O4" s="21" t="n">
-        <v>4.530791803013039</v>
+        <v>4.537161792469527</v>
       </c>
       <c r="P4" s="21" t="n">
         <v>2.99625468164794</v>
@@ -1666,11 +1666,11 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O5" s="26" t="n">
-        <v>1.00676649112446</v>
+        <v>1.008181937300853</v>
       </c>
       <c r="P5" s="26" t="n">
         <v>0.8595988538681949</v>
@@ -1700,13 +1700,13 @@
         <v>30.55</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="H6" s="18" t="n">
         <v>1218456.2</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>1256346</v>
+        <v>1246375</v>
       </c>
       <c r="J6" s="20" t="n">
         <v>79768</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="L6" s="18" t="n">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
@@ -1726,14 +1726,14 @@
       </c>
       <c r="N6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>8.695258304860658</v>
+        <v>8.638376245004611</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>3.10965630114566</v>
+        <v>2.291325695581012</v>
       </c>
     </row>
     <row r="7">
@@ -1760,13 +1760,13 @@
         <v>360</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>387</v>
+        <v>371.5</v>
       </c>
       <c r="H7" s="23" t="n">
         <v>811080</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>871911</v>
+        <v>836989.5</v>
       </c>
       <c r="J7" s="25" t="n">
         <v>4506</v>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="L7" s="23" t="n">
-        <v>387</v>
+        <v>371.5</v>
       </c>
       <c r="M7" s="23" t="inlineStr">
         <is>
@@ -1786,14 +1786,14 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O7" s="26" t="n">
-        <v>6.034556852848945</v>
+        <v>5.801007091861027</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>7.5</v>
+        <v>3.194444444444444</v>
       </c>
     </row>
     <row r="8">
@@ -1820,13 +1820,13 @@
         <v>4.19</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>436388.5000000001</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>437430</v>
+        <v>435346.9999999999</v>
       </c>
       <c r="J8" s="20" t="n">
         <v>208299.9999999999</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="L8" s="18" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="M8" s="18" t="inlineStr">
         <is>
@@ -1846,14 +1846,14 @@
       </c>
       <c r="N8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>3.027483543781091</v>
+        <v>3.017303125571375</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>0.2386634844868684</v>
+        <v>-0.2386634844868896</v>
       </c>
     </row>
     <row r="9">
@@ -1880,13 +1880,13 @@
         <v>12.85</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>373832.2</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>354922.4</v>
+        <v>362195.4</v>
       </c>
       <c r="J9" s="25" t="n">
         <v>58184</v>
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="L9" s="23" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
@@ -1906,14 +1906,14 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O9" s="26" t="n">
-        <v>2.456442688702854</v>
+        <v>2.510303993107967</v>
       </c>
       <c r="P9" s="26" t="n">
-        <v>-5.058365758754866</v>
+        <v>-3.112840466926073</v>
       </c>
     </row>
     <row r="10">
@@ -1940,13 +1940,13 @@
         <v>9.18</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>9.1</v>
+        <v>9.08</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>410869.26</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>407288.7</v>
+        <v>406393.56</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>89514</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="L10" s="18" t="n">
-        <v>9.1</v>
+        <v>9.08</v>
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
@@ -1966,14 +1966,14 @@
       </c>
       <c r="N10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>2.81887350391604</v>
+        <v>2.816632614443371</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>-0.8714596949891076</v>
+        <v>-1.08932461873638</v>
       </c>
     </row>
     <row r="11">
@@ -2000,13 +2000,13 @@
         <v>15.35</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>16</v>
+        <v>15.95</v>
       </c>
       <c r="H11" s="23" t="n">
         <v>765166.7999999999</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>797568</v>
+        <v>795075.6</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>99696.00000000012</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="L11" s="23" t="n">
-        <v>16</v>
+        <v>15.95</v>
       </c>
       <c r="M11" s="23" t="inlineStr">
         <is>
@@ -2026,14 +2026,14 @@
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O11" s="26" t="n">
-        <v>5.520023763908275</v>
+        <v>5.510510220457557</v>
       </c>
       <c r="P11" s="26" t="n">
-        <v>4.23452768729642</v>
+        <v>3.908794788273613</v>
       </c>
     </row>
     <row r="12">
@@ -2060,13 +2060,13 @@
         <v>55.5</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>47.05</v>
+        <v>48.05</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>943777.5</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>800085.25</v>
+        <v>817090.25</v>
       </c>
       <c r="J12" s="20" t="n">
         <v>34010</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="L12" s="18" t="n">
-        <v>47.05</v>
+        <v>48.05</v>
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
@@ -2086,14 +2086,14 @@
       </c>
       <c r="N12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>5.537445826753949</v>
+        <v>5.663089363654501</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>-15.22522522522523</v>
+        <v>-13.42342342342343</v>
       </c>
     </row>
     <row r="13">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr"/>
       <c r="O13" s="26" t="n">
-        <v>9.400833682302322</v>
+        <v>9.414050624073656</v>
       </c>
       <c r="P13" s="26" t="n">
         <v>0.003828483920367535</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N14" s="18" t="inlineStr"/>
       <c r="O14" s="21" t="n">
-        <v>3.968195345145253</v>
+        <v>3.973774361707668</v>
       </c>
       <c r="P14" s="21" t="n">
         <v>0.01744439598778892</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr"/>
       <c r="O15" s="26" t="n">
-        <v>25.6079581007019</v>
+        <v>25.64396117261423</v>
       </c>
       <c r="P15" s="26" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="N16" s="18" t="inlineStr"/>
       <c r="O16" s="21" t="n">
-        <v>13.84213951389292</v>
+        <v>13.86160063384553</v>
       </c>
       <c r="P16" s="21" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>583841.5</v>
+        <v>589641.25</v>
       </c>
       <c r="H3" s="23" t="n">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>1256346</v>
+        <v>1246375</v>
       </c>
       <c r="H6" s="18" t="n">
         <v>0</v>
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>871911</v>
+        <v>836989.5</v>
       </c>
       <c r="H7" s="23" t="n">
         <v>0</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>437430</v>
+        <v>435346.9999999999</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>354922.4</v>
+        <v>362195.4</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>407288.7</v>
+        <v>406393.56</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>800085.25</v>
+        <v>817090.25</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>0</v>
@@ -2760,11 +2760,11 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="B2" s="20" t="n">
-        <v>14448633.45</v>
+        <v>14428348.16</v>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>75.5</v>
+        <v>76.25</v>
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" s="20" t="n">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>387</v>
+        <v>371.5</v>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="C8" s="20" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>9.1</v>
+        <v>9.08</v>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>16</v>
+        <v>15.95</v>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C12" s="20" t="n">
-        <v>47.05</v>
+        <v>48.05</v>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:26</t>
+          <t>2026-06-04 08:16:34</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
@@ -3440,7 +3440,7 @@
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B3" s="22" t="inlineStr">
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="25" t="n">
-        <v>9666.25</v>
+        <v>15466</v>
       </c>
       <c r="K3" s="25" t="n">
         <v>574175.25</v>
@@ -3487,7 +3487,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -3534,7 +3534,7 @@
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
@@ -3581,7 +3581,7 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>37889.80000000005</v>
+        <v>27918.80000000005</v>
       </c>
       <c r="K6" s="20" t="n">
         <v>1218456.2</v>
@@ -3628,7 +3628,7 @@
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="25" t="n">
-        <v>60831</v>
+        <v>25909.5</v>
       </c>
       <c r="K7" s="25" t="n">
         <v>811080</v>
@@ -3675,7 +3675,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>1041.499999999942</v>
+        <v>-1041.500000000116</v>
       </c>
       <c r="K8" s="20" t="n">
         <v>436388.5000000001</v>
@@ -3722,7 +3722,7 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
@@ -3754,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="25" t="n">
-        <v>-18909.80000000005</v>
+        <v>-11636.80000000005</v>
       </c>
       <c r="K9" s="25" t="n">
         <v>373832.2</v>
@@ -3769,7 +3769,7 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>-3580.559999999998</v>
+        <v>-4475.700000000012</v>
       </c>
       <c r="K10" s="20" t="n">
         <v>410869.26</v>
@@ -3816,7 +3816,7 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>32401.20000000007</v>
+        <v>29908.80000000005</v>
       </c>
       <c r="K11" s="25" t="n">
         <v>765166.7999999999</v>
@@ -3863,7 +3863,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>-143692.25</v>
+        <v>-126687.25</v>
       </c>
       <c r="K12" s="20" t="n">
         <v>943777.5</v>
@@ -3910,7 +3910,7 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
@@ -4004,7 +4004,7 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>2026-06-03 10:17:43</t>
+          <t>2026-06-04 08:16:52</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -4183,10 +4183,10 @@
         <v>74.25</v>
       </c>
       <c r="E3" t="n">
-        <v>75.5</v>
+        <v>76.25</v>
       </c>
       <c r="F3" t="n">
-        <v>583841.5</v>
+        <v>589641.25</v>
       </c>
     </row>
     <row r="4">
@@ -4255,10 +4255,10 @@
         <v>30.55</v>
       </c>
       <c r="E6" t="n">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1256346</v>
+        <v>1246375</v>
       </c>
     </row>
     <row r="7">
@@ -4279,10 +4279,10 @@
         <v>360</v>
       </c>
       <c r="E7" t="n">
-        <v>387</v>
+        <v>371.5</v>
       </c>
       <c r="F7" t="n">
-        <v>871911</v>
+        <v>836989.5</v>
       </c>
     </row>
     <row r="8">
@@ -4303,10 +4303,10 @@
         <v>4.19</v>
       </c>
       <c r="E8" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="F8" t="n">
-        <v>437430</v>
+        <v>435346.9999999999</v>
       </c>
     </row>
     <row r="9">
@@ -4327,10 +4327,10 @@
         <v>12.85</v>
       </c>
       <c r="E9" t="n">
-        <v>12.2</v>
+        <v>12.45</v>
       </c>
       <c r="F9" t="n">
-        <v>354922.4</v>
+        <v>362195.4</v>
       </c>
     </row>
     <row r="10">
@@ -4351,10 +4351,10 @@
         <v>9.18</v>
       </c>
       <c r="E10" t="n">
-        <v>9.1</v>
+        <v>9.08</v>
       </c>
       <c r="F10" t="n">
-        <v>407288.7</v>
+        <v>406393.56</v>
       </c>
     </row>
     <row r="11">
@@ -4375,10 +4375,10 @@
         <v>15.35</v>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>15.95</v>
       </c>
       <c r="F11" t="n">
-        <v>797568</v>
+        <v>795075.6</v>
       </c>
     </row>
     <row r="12">
@@ -4399,10 +4399,10 @@
         <v>55.5</v>
       </c>
       <c r="E12" t="n">
-        <v>47.05</v>
+        <v>48.05</v>
       </c>
       <c r="F12" t="n">
-        <v>800085.25</v>
+        <v>817090.25</v>
       </c>
     </row>
     <row r="13">

--- a/reports/Lawrence_Client1_Kenya_Dashboard_Output.xlsx
+++ b/reports/Lawrence_Client1_Kenya_Dashboard_Output.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>14428348.16</v>
+        <v>14493416.45</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>507497.1</v>
+        <v>505906.2</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.517361061517384</v>
+        <v>3.490593137548325</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>589641.25</v>
+        <v>599307.5</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4.086685762370736</v>
+        <v>4.135032634075729</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -892,7 +892,7 @@
         <v>654637.5</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.537161792469527</v>
+        <v>4.51679217428407</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>145464</v>
+        <v>146703.75</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1.008181937300853</v>
+        <v>1.012209581544178</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1246375</v>
+        <v>1254351.8</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8.638376245004611</v>
+        <v>8.654631599991044</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>836989.5</v>
+        <v>894441</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>5.801007091861027</v>
+        <v>6.171360652511989</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>435346.9999999999</v>
+        <v>436388.5000000001</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3.017303125571375</v>
+        <v>3.010942944373892</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -957,7 +957,7 @@
         <v>362195.4</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.510303993107967</v>
+        <v>2.499033966556587</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>406393.56</v>
+        <v>407288.7</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2.816632614443371</v>
+        <v>2.810163507031498</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -980,10 +980,10 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>795075.6</v>
+        <v>782613.6</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5.510510220457557</v>
+        <v>5.399786880477032</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>817090.25</v>
+        <v>817940.5</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5.663089363654501</v>
+        <v>5.64353134281186</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1009,7 +1009,7 @@
         <v>1358292</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9.414050624073656</v>
+        <v>9.371786180890428</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>573350</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3.973774361707668</v>
+        <v>3.955934075157276</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1035,7 +1035,7 @@
         <v>3700000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>25.64396117261423</v>
+        <v>25.52883243757203</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1048,7 +1048,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>13.86160063384553</v>
+        <v>13.79936888517407</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>13.1493905536585</v>
+        <v>13.1546275274523</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>13.86160063384553</v>
+        <v>13.79936888517407</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>13.38782498578132</v>
+        <v>13.3277202560477</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>13.99023219855543</v>
+        <v>13.85348173032039</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>25.64396117261423</v>
+        <v>25.52883243757203</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>11.32861421054037</v>
+        <v>11.68133756344247</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>8.638376245004611</v>
+        <v>8.654631599991044</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1462,13 +1462,13 @@
         <v>32.1</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="H2" s="18" t="n">
         <v>510678.9</v>
       </c>
       <c r="I2" s="20" t="n">
-        <v>507497.1</v>
+        <v>505906.2</v>
       </c>
       <c r="J2" s="20" t="n">
         <v>31818</v>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="L2" s="18" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="M2" s="18" t="inlineStr">
         <is>
@@ -1488,14 +1488,14 @@
       </c>
       <c r="N2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O2" s="21" t="n">
-        <v>3.517361061517384</v>
+        <v>3.490593137548325</v>
       </c>
       <c r="P2" s="21" t="n">
-        <v>-0.6230529595015665</v>
+        <v>-0.9345794392523387</v>
       </c>
     </row>
     <row r="3">
@@ -1522,13 +1522,13 @@
         <v>74.25</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>76.25</v>
+        <v>77.5</v>
       </c>
       <c r="H3" s="23" t="n">
         <v>574175.25</v>
       </c>
       <c r="I3" s="25" t="n">
-        <v>589641.25</v>
+        <v>599307.5</v>
       </c>
       <c r="J3" s="25" t="n">
         <v>15466</v>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="L3" s="23" t="n">
-        <v>76.25</v>
+        <v>77.5</v>
       </c>
       <c r="M3" s="23" t="inlineStr">
         <is>
@@ -1548,14 +1548,14 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O3" s="26" t="n">
-        <v>4.086685762370736</v>
+        <v>4.135032634075729</v>
       </c>
       <c r="P3" s="26" t="n">
-        <v>2.693602693602693</v>
+        <v>4.377104377104377</v>
       </c>
     </row>
     <row r="4">
@@ -1606,11 +1606,11 @@
       </c>
       <c r="N4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O4" s="21" t="n">
-        <v>4.537161792469527</v>
+        <v>4.51679217428407</v>
       </c>
       <c r="P4" s="21" t="n">
         <v>2.99625468164794</v>
@@ -1640,13 +1640,13 @@
         <v>87.25</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>88</v>
+        <v>88.75</v>
       </c>
       <c r="H5" s="23" t="n">
         <v>144224.25</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>145464</v>
+        <v>146703.75</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>3306</v>
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="L5" s="23" t="n">
-        <v>88</v>
+        <v>88.75</v>
       </c>
       <c r="M5" s="23" t="inlineStr">
         <is>
@@ -1666,14 +1666,14 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O5" s="26" t="n">
-        <v>1.008181937300853</v>
+        <v>1.012209581544178</v>
       </c>
       <c r="P5" s="26" t="n">
-        <v>0.8595988538681949</v>
+        <v>1.71919770773639</v>
       </c>
     </row>
     <row r="6">
@@ -1700,13 +1700,13 @@
         <v>30.55</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>31.25</v>
+        <v>31.45</v>
       </c>
       <c r="H6" s="18" t="n">
         <v>1218456.2</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>1246375</v>
+        <v>1254351.8</v>
       </c>
       <c r="J6" s="20" t="n">
         <v>79768</v>
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="L6" s="18" t="n">
-        <v>31.25</v>
+        <v>31.45</v>
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
@@ -1726,14 +1726,14 @@
       </c>
       <c r="N6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>8.638376245004611</v>
+        <v>8.654631599991044</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>2.291325695581012</v>
+        <v>2.945990180032728</v>
       </c>
     </row>
     <row r="7">
@@ -1760,13 +1760,13 @@
         <v>360</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>371.5</v>
+        <v>397</v>
       </c>
       <c r="H7" s="23" t="n">
         <v>811080</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>836989.5</v>
+        <v>894441</v>
       </c>
       <c r="J7" s="25" t="n">
         <v>4506</v>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="L7" s="23" t="n">
-        <v>371.5</v>
+        <v>397</v>
       </c>
       <c r="M7" s="23" t="inlineStr">
         <is>
@@ -1786,14 +1786,14 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O7" s="26" t="n">
-        <v>5.801007091861027</v>
+        <v>6.171360652511989</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>3.194444444444444</v>
+        <v>10.27777777777778</v>
       </c>
     </row>
     <row r="8">
@@ -1820,13 +1820,13 @@
         <v>4.19</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>436388.5000000001</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>435346.9999999999</v>
+        <v>436388.5000000001</v>
       </c>
       <c r="J8" s="20" t="n">
         <v>208299.9999999999</v>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="L8" s="18" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="M8" s="18" t="inlineStr">
         <is>
@@ -1846,14 +1846,14 @@
       </c>
       <c r="N8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>3.017303125571375</v>
+        <v>3.010942944373892</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>-0.2386634844868896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1906,11 +1906,11 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O9" s="26" t="n">
-        <v>2.510303993107967</v>
+        <v>2.499033966556587</v>
       </c>
       <c r="P9" s="26" t="n">
         <v>-3.112840466926073</v>
@@ -1940,13 +1940,13 @@
         <v>9.18</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>410869.26</v>
       </c>
       <c r="I10" s="20" t="n">
-        <v>406393.56</v>
+        <v>407288.7</v>
       </c>
       <c r="J10" s="20" t="n">
         <v>89514</v>
@@ -1957,7 +1957,7 @@
         </is>
       </c>
       <c r="L10" s="18" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="M10" s="18" t="inlineStr">
         <is>
@@ -1966,14 +1966,14 @@
       </c>
       <c r="N10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>2.816632614443371</v>
+        <v>2.810163507031498</v>
       </c>
       <c r="P10" s="21" t="n">
-        <v>-1.08932461873638</v>
+        <v>-0.8714596949891076</v>
       </c>
     </row>
     <row r="11">
@@ -2000,13 +2000,13 @@
         <v>15.35</v>
       </c>
       <c r="G11" s="25" t="n">
-        <v>15.95</v>
+        <v>15.7</v>
       </c>
       <c r="H11" s="23" t="n">
         <v>765166.7999999999</v>
       </c>
       <c r="I11" s="25" t="n">
-        <v>795075.6</v>
+        <v>782613.6</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>99696.00000000012</v>
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="L11" s="23" t="n">
-        <v>15.95</v>
+        <v>15.7</v>
       </c>
       <c r="M11" s="23" t="inlineStr">
         <is>
@@ -2026,14 +2026,14 @@
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O11" s="26" t="n">
-        <v>5.510510220457557</v>
+        <v>5.399786880477032</v>
       </c>
       <c r="P11" s="26" t="n">
-        <v>3.908794788273613</v>
+        <v>2.280130293159607</v>
       </c>
     </row>
     <row r="12">
@@ -2060,13 +2060,13 @@
         <v>55.5</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>48.05</v>
+        <v>48.1</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>943777.5</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>817090.25</v>
+        <v>817940.5</v>
       </c>
       <c r="J12" s="20" t="n">
         <v>34010</v>
@@ -2077,7 +2077,7 @@
         </is>
       </c>
       <c r="L12" s="18" t="n">
-        <v>48.05</v>
+        <v>48.1</v>
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
@@ -2086,14 +2086,14 @@
       </c>
       <c r="N12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>5.663089363654501</v>
+        <v>5.64353134281186</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>-13.42342342342343</v>
+        <v>-13.33333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr"/>
       <c r="O13" s="26" t="n">
-        <v>9.414050624073656</v>
+        <v>9.371786180890428</v>
       </c>
       <c r="P13" s="26" t="n">
         <v>0.003828483920367535</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N14" s="18" t="inlineStr"/>
       <c r="O14" s="21" t="n">
-        <v>3.973774361707668</v>
+        <v>3.955934075157276</v>
       </c>
       <c r="P14" s="21" t="n">
         <v>0.01744439598778892</v>
@@ -2240,7 +2240,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr"/>
       <c r="O15" s="26" t="n">
-        <v>25.64396117261423</v>
+        <v>25.52883243757203</v>
       </c>
       <c r="P15" s="26" t="n">
         <v>0</v>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="N16" s="18" t="inlineStr"/>
       <c r="O16" s="21" t="n">
-        <v>13.86160063384553</v>
+        <v>13.79936888517407</v>
       </c>
       <c r="P16" s="21" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>507497.1</v>
+        <v>505906.2</v>
       </c>
       <c r="H2" s="18" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>589641.25</v>
+        <v>599307.5</v>
       </c>
       <c r="H3" s="23" t="n">
         <v>0</v>
@@ -2443,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>145464</v>
+        <v>146703.75</v>
       </c>
       <c r="H5" s="23" t="n">
         <v>0</v>
@@ -2465,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>1246375</v>
+        <v>1254351.8</v>
       </c>
       <c r="H6" s="18" t="n">
         <v>0</v>
@@ -2487,7 +2487,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>836989.5</v>
+        <v>894441</v>
       </c>
       <c r="H7" s="23" t="n">
         <v>0</v>
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>435346.9999999999</v>
+        <v>436388.5000000001</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>406393.56</v>
+        <v>407288.7</v>
       </c>
       <c r="H10" s="18" t="n">
         <v>0</v>
@@ -2595,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>817090.25</v>
+        <v>817940.5</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>0</v>
@@ -2760,11 +2760,11 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="B2" s="20" t="n">
-        <v>14428348.16</v>
+        <v>14493416.45</v>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
@@ -2963,7 +2963,7 @@
         </is>
       </c>
       <c r="C2" s="20" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="E2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>76.25</v>
+        <v>77.5</v>
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
@@ -2997,7 +2997,7 @@
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>88</v>
+        <v>88.75</v>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3063,7 @@
         </is>
       </c>
       <c r="C6" s="20" t="n">
-        <v>31.25</v>
+        <v>31.45</v>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>371.5</v>
+        <v>397</v>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="C8" s="20" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="C10" s="20" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
         </is>
       </c>
       <c r="C11" s="25" t="n">
-        <v>15.95</v>
+        <v>15.7</v>
       </c>
       <c r="D11" s="23" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3213,7 @@
         </is>
       </c>
       <c r="C12" s="20" t="n">
-        <v>48.05</v>
+        <v>48.1</v>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:34</t>
+          <t>2026-06-05 02:02:19</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3393,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="20" t="n">
-        <v>-3181.800000000047</v>
+        <v>-4772.700000000012</v>
       </c>
       <c r="K2" s="20" t="n">
         <v>510678.9</v>
@@ -3440,7 +3440,7 @@
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B3" s="22" t="inlineStr">
@@ -3472,7 +3472,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="25" t="n">
-        <v>15466</v>
+        <v>25132.25</v>
       </c>
       <c r="K3" s="25" t="n">
         <v>574175.25</v>
@@ -3487,7 +3487,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -3534,7 +3534,7 @@
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
@@ -3566,7 +3566,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>1239.75</v>
+        <v>2479.5</v>
       </c>
       <c r="K5" s="25" t="n">
         <v>144224.25</v>
@@ -3581,7 +3581,7 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>27918.80000000005</v>
+        <v>35895.60000000009</v>
       </c>
       <c r="K6" s="20" t="n">
         <v>1218456.2</v>
@@ -3628,7 +3628,7 @@
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
@@ -3660,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="25" t="n">
-        <v>25909.5</v>
+        <v>83361</v>
       </c>
       <c r="K7" s="25" t="n">
         <v>811080</v>
@@ -3675,7 +3675,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
@@ -3707,7 +3707,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>-1041.500000000116</v>
+        <v>0</v>
       </c>
       <c r="K8" s="20" t="n">
         <v>436388.5000000001</v>
@@ -3722,7 +3722,7 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
@@ -3769,7 +3769,7 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -3801,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="20" t="n">
-        <v>-4475.700000000012</v>
+        <v>-3580.559999999998</v>
       </c>
       <c r="K10" s="20" t="n">
         <v>410869.26</v>
@@ -3816,7 +3816,7 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
@@ -3848,7 +3848,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="25" t="n">
-        <v>29908.80000000005</v>
+        <v>17446.80000000005</v>
       </c>
       <c r="K11" s="25" t="n">
         <v>765166.7999999999</v>
@@ -3863,7 +3863,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -3895,7 +3895,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>-126687.25</v>
+        <v>-125837</v>
       </c>
       <c r="K12" s="20" t="n">
         <v>943777.5</v>
@@ -3910,7 +3910,7 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -3957,7 +3957,7 @@
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
@@ -4004,7 +4004,7 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>2026-06-04 08:16:52</t>
+          <t>2026-06-05 02:02:37</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -4159,10 +4159,10 @@
         <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="F2" t="n">
-        <v>507497.1</v>
+        <v>505906.2</v>
       </c>
     </row>
     <row r="3">
@@ -4183,10 +4183,10 @@
         <v>74.25</v>
       </c>
       <c r="E3" t="n">
-        <v>76.25</v>
+        <v>77.5</v>
       </c>
       <c r="F3" t="n">
-        <v>589641.25</v>
+        <v>599307.5</v>
       </c>
     </row>
     <row r="4">
@@ -4231,10 +4231,10 @@
         <v>87.25</v>
       </c>
       <c r="E5" t="n">
-        <v>88</v>
+        <v>88.75</v>
       </c>
       <c r="F5" t="n">
-        <v>145464</v>
+        <v>146703.75</v>
       </c>
     </row>
     <row r="6">
@@ -4255,10 +4255,10 @@
         <v>30.55</v>
       </c>
       <c r="E6" t="n">
-        <v>31.25</v>
+        <v>31.45</v>
       </c>
       <c r="F6" t="n">
-        <v>1246375</v>
+        <v>1254351.8</v>
       </c>
     </row>
     <row r="7">
@@ -4279,10 +4279,10 @@
         <v>360</v>
       </c>
       <c r="E7" t="n">
-        <v>371.5</v>
+        <v>397</v>
       </c>
       <c r="F7" t="n">
-        <v>836989.5</v>
+        <v>894441</v>
       </c>
     </row>
     <row r="8">
@@ -4303,10 +4303,10 @@
         <v>4.19</v>
       </c>
       <c r="E8" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="F8" t="n">
-        <v>435346.9999999999</v>
+        <v>436388.5000000001</v>
       </c>
     </row>
     <row r="9">
@@ -4351,10 +4351,10 @@
         <v>9.18</v>
       </c>
       <c r="E10" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="F10" t="n">
-        <v>406393.56</v>
+        <v>407288.7</v>
       </c>
     </row>
     <row r="11">
@@ -4375,10 +4375,10 @@
         <v>15.35</v>
       </c>
       <c r="E11" t="n">
-        <v>15.95</v>
+        <v>15.7</v>
       </c>
       <c r="F11" t="n">
-        <v>795075.6</v>
+        <v>782613.6</v>
       </c>
     </row>
     <row r="12">
@@ -4399,10 +4399,10 @@
         <v>55.5</v>
       </c>
       <c r="E12" t="n">
-        <v>48.05</v>
+        <v>48.1</v>
       </c>
       <c r="F12" t="n">
-        <v>817090.25</v>
+        <v>817940.5</v>
       </c>
     </row>
     <row r="13">

--- a/reports/Lawrence_Client1_Kenya_Dashboard_Output.xlsx
+++ b/reports/Lawrence_Client1_Kenya_Dashboard_Output.xlsx
@@ -814,7 +814,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>14493416.45</v>
+        <v>14541450.55</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>505906.2</v>
+        <v>542496.9</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>3.490593137548325</v>
+        <v>3.730693152891821</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -876,10 +876,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>599307.5</v>
+        <v>597374.25</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4.135032634075729</v>
+        <v>4.108078818863087</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -892,7 +892,7 @@
         <v>654637.5</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.51679217428407</v>
+        <v>4.501872063925562</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>146703.75</v>
+        <v>145464</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1.012209581544178</v>
+        <v>1.0003403683823</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -915,10 +915,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>1254351.8</v>
+        <v>1264322.8</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>8.654631599991044</v>
+        <v>8.694612656782029</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>894441</v>
+        <v>901200</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6.171360652511989</v>
+        <v>6.197456002764456</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>436388.5000000001</v>
+        <v>437430</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>3.010942944373892</v>
+        <v>3.008159320116795</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>362195.4</v>
+        <v>360740.8</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.499033966556587</v>
+        <v>2.480775894809201</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -970,7 +970,7 @@
         <v>407288.7</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>2.810163507031498</v>
+        <v>2.800880824093577</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -983,7 +983,7 @@
         <v>782613.6</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>5.399786880477032</v>
+        <v>5.381950014608412</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>817940.5</v>
+        <v>816240</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>5.64353134281186</v>
+        <v>5.613195170546448</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -1009,7 +1009,7 @@
         <v>1358292</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9.371786180890428</v>
+        <v>9.340828793727184</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -1022,7 +1022,7 @@
         <v>573350</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3.955934075157276</v>
+        <v>3.942866621377054</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -1035,7 +1035,7 @@
         <v>3700000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>25.52883243757203</v>
+        <v>25.44450422794994</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1048,7 +1048,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>13.79936888517407</v>
+        <v>13.75378606916213</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>13.1546275274523</v>
+        <v>13.34098440406277</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>13.79936888517407</v>
+        <v>13.75378606916213</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>13.3277202560477</v>
+        <v>13.28369541510424</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>13.85348173032039</v>
+        <v>13.79602600924844</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>25.52883243757203</v>
+        <v>25.44450422794994</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>11.68133756344247</v>
+        <v>11.68639121769045</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>8.654631599991044</v>
+        <v>8.694612656782029</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1462,13 +1462,13 @@
         <v>32.1</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>31.8</v>
+        <v>34.1</v>
       </c>
       <c r="H2" s="18" t="n">
         <v>510678.9</v>
       </c>
       <c r="I2" s="20" t="n">
-        <v>505906.2</v>
+        <v>542496.9</v>
       </c>
       <c r="J2" s="20" t="n">
         <v>31818</v>
@@ -1478,24 +1478,22 @@
           <t>COOP</t>
         </is>
       </c>
-      <c r="L2" s="18" t="n">
-        <v>31.8</v>
-      </c>
+      <c r="L2" s="18" t="inlineStr"/>
       <c r="M2" s="18" t="inlineStr">
         <is>
-          <t>NSE live market data</t>
+          <t>NSE live market data unavailable</t>
         </is>
       </c>
       <c r="N2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O2" s="21" t="n">
-        <v>3.490593137548325</v>
+        <v>3.730693152891821</v>
       </c>
       <c r="P2" s="21" t="n">
-        <v>-0.9345794392523387</v>
+        <v>6.230529595015576</v>
       </c>
     </row>
     <row r="3">
@@ -1522,13 +1520,13 @@
         <v>74.25</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>77.5</v>
+        <v>77.25</v>
       </c>
       <c r="H3" s="23" t="n">
         <v>574175.25</v>
       </c>
       <c r="I3" s="25" t="n">
-        <v>599307.5</v>
+        <v>597374.25</v>
       </c>
       <c r="J3" s="25" t="n">
         <v>15466</v>
@@ -1539,7 +1537,7 @@
         </is>
       </c>
       <c r="L3" s="23" t="n">
-        <v>77.5</v>
+        <v>77.25</v>
       </c>
       <c r="M3" s="23" t="inlineStr">
         <is>
@@ -1548,14 +1546,14 @@
       </c>
       <c r="N3" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O3" s="26" t="n">
-        <v>4.135032634075729</v>
+        <v>4.108078818863087</v>
       </c>
       <c r="P3" s="26" t="n">
-        <v>4.377104377104377</v>
+        <v>4.040404040404041</v>
       </c>
     </row>
     <row r="4">
@@ -1606,11 +1604,11 @@
       </c>
       <c r="N4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O4" s="21" t="n">
-        <v>4.51679217428407</v>
+        <v>4.501872063925562</v>
       </c>
       <c r="P4" s="21" t="n">
         <v>2.99625468164794</v>
@@ -1640,13 +1638,13 @@
         <v>87.25</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>88.75</v>
+        <v>88</v>
       </c>
       <c r="H5" s="23" t="n">
         <v>144224.25</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>146703.75</v>
+        <v>145464</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>3306</v>
@@ -1657,7 +1655,7 @@
         </is>
       </c>
       <c r="L5" s="23" t="n">
-        <v>88.75</v>
+        <v>88</v>
       </c>
       <c r="M5" s="23" t="inlineStr">
         <is>
@@ -1666,14 +1664,14 @@
       </c>
       <c r="N5" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O5" s="26" t="n">
-        <v>1.012209581544178</v>
+        <v>1.0003403683823</v>
       </c>
       <c r="P5" s="26" t="n">
-        <v>1.71919770773639</v>
+        <v>0.8595988538681949</v>
       </c>
     </row>
     <row r="6">
@@ -1700,13 +1698,13 @@
         <v>30.55</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>31.45</v>
+        <v>31.7</v>
       </c>
       <c r="H6" s="18" t="n">
         <v>1218456.2</v>
       </c>
       <c r="I6" s="20" t="n">
-        <v>1254351.8</v>
+        <v>1264322.8</v>
       </c>
       <c r="J6" s="20" t="n">
         <v>79768</v>
@@ -1717,7 +1715,7 @@
         </is>
       </c>
       <c r="L6" s="18" t="n">
-        <v>31.45</v>
+        <v>31.7</v>
       </c>
       <c r="M6" s="18" t="inlineStr">
         <is>
@@ -1726,14 +1724,14 @@
       </c>
       <c r="N6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O6" s="21" t="n">
-        <v>8.654631599991044</v>
+        <v>8.694612656782029</v>
       </c>
       <c r="P6" s="21" t="n">
-        <v>2.945990180032728</v>
+        <v>3.764320785597377</v>
       </c>
     </row>
     <row r="7">
@@ -1760,13 +1758,13 @@
         <v>360</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="H7" s="23" t="n">
         <v>811080</v>
       </c>
       <c r="I7" s="25" t="n">
-        <v>894441</v>
+        <v>901200</v>
       </c>
       <c r="J7" s="25" t="n">
         <v>4506</v>
@@ -1777,7 +1775,7 @@
         </is>
       </c>
       <c r="L7" s="23" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="M7" s="23" t="inlineStr">
         <is>
@@ -1786,14 +1784,14 @@
       </c>
       <c r="N7" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O7" s="26" t="n">
-        <v>6.171360652511989</v>
+        <v>6.197456002764456</v>
       </c>
       <c r="P7" s="26" t="n">
-        <v>10.27777777777778</v>
+        <v>11.11111111111111</v>
       </c>
     </row>
     <row r="8">
@@ -1820,13 +1818,13 @@
         <v>4.19</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>436388.5000000001</v>
       </c>
       <c r="I8" s="20" t="n">
-        <v>436388.5000000001</v>
+        <v>437430</v>
       </c>
       <c r="J8" s="20" t="n">
         <v>208299.9999999999</v>
@@ -1837,7 +1835,7 @@
         </is>
       </c>
       <c r="L8" s="18" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="M8" s="18" t="inlineStr">
         <is>
@@ -1846,14 +1844,14 @@
       </c>
       <c r="N8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O8" s="21" t="n">
-        <v>3.010942944373892</v>
+        <v>3.008159320116795</v>
       </c>
       <c r="P8" s="21" t="n">
-        <v>0</v>
+        <v>0.2386634844868684</v>
       </c>
     </row>
     <row r="9">
@@ -1880,13 +1878,13 @@
         <v>12.85</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>373832.2</v>
       </c>
       <c r="I9" s="25" t="n">
-        <v>362195.4</v>
+        <v>360740.8</v>
       </c>
       <c r="J9" s="25" t="n">
         <v>58184</v>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="L9" s="23" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="M9" s="23" t="inlineStr">
         <is>
@@ -1906,14 +1904,14 @@
       </c>
       <c r="N9" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O9" s="26" t="n">
-        <v>2.499033966556587</v>
+        <v>2.480775894809201</v>
       </c>
       <c r="P9" s="26" t="n">
-        <v>-3.112840466926073</v>
+        <v>-3.501945525291823</v>
       </c>
     </row>
     <row r="10">
@@ -1966,11 +1964,11 @@
       </c>
       <c r="N10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O10" s="21" t="n">
-        <v>2.810163507031498</v>
+        <v>2.800880824093577</v>
       </c>
       <c r="P10" s="21" t="n">
         <v>-0.8714596949891076</v>
@@ -2026,11 +2024,11 @@
       </c>
       <c r="N11" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O11" s="26" t="n">
-        <v>5.399786880477032</v>
+        <v>5.381950014608412</v>
       </c>
       <c r="P11" s="26" t="n">
         <v>2.280130293159607</v>
@@ -2060,13 +2058,13 @@
         <v>55.5</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>943777.5</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>817940.5</v>
+        <v>816240</v>
       </c>
       <c r="J12" s="20" t="n">
         <v>34010</v>
@@ -2077,7 +2075,7 @@
         </is>
       </c>
       <c r="L12" s="18" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="M12" s="18" t="inlineStr">
         <is>
@@ -2086,14 +2084,14 @@
       </c>
       <c r="N12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
       <c r="O12" s="21" t="n">
-        <v>5.64353134281186</v>
+        <v>5.613195170546448</v>
       </c>
       <c r="P12" s="21" t="n">
-        <v>-13.33333333333333</v>
+        <v>-13.51351351351351</v>
       </c>
     </row>
     <row r="13">
@@ -2140,7 +2138,7 @@
       </c>
       <c r="N13" s="23" t="inlineStr"/>
       <c r="O13" s="26" t="n">
-        <v>9.371786180890428</v>
+        <v>9.340828793727184</v>
       </c>
       <c r="P13" s="26" t="n">
         <v>0.003828483920367535</v>
@@ -2190,7 +2188,7 @@
       </c>
       <c r="N14" s="18" t="inlineStr"/>
       <c r="O14" s="21" t="n">
-        <v>3.955934075157276</v>
+        <v>3.942866621377054</v>
       </c>
       <c r="P14" s="21" t="n">
         <v>0.01744439598778892</v>
@@ -2240,7 +2238,7 @@
       </c>
       <c r="N15" s="23" t="inlineStr"/>
       <c r="O15" s="26" t="n">
-        <v>25.52883243757203</v>
+        <v>25.44450422794994</v>
       </c>
       <c r="P15" s="26" t="n">
         <v>0</v>
@@ -2290,7 +2288,7 @@
       </c>
       <c r="N16" s="18" t="inlineStr"/>
       <c r="O16" s="21" t="n">
-        <v>13.79936888517407</v>
+        <v>13.75378606916213</v>
       </c>
       <c r="P16" s="21" t="n">
         <v>0</v>
@@ -2377,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="G2" s="20" t="n">
-        <v>505906.2</v>
+        <v>542496.9</v>
       </c>
       <c r="H2" s="18" t="n">
         <v>0</v>
@@ -2399,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="25" t="n">
-        <v>599307.5</v>
+        <v>597374.25</v>
       </c>
       <c r="H3" s="23" t="n">
         <v>0</v>
@@ -2443,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>146703.75</v>
+        <v>145464</v>
       </c>
       <c r="H5" s="23" t="n">
         <v>0</v>
@@ -2465,7 +2463,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>1254351.8</v>
+        <v>1264322.8</v>
       </c>
       <c r="H6" s="18" t="n">
         <v>0</v>
@@ -2487,7 +2485,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>894441</v>
+        <v>901200</v>
       </c>
       <c r="H7" s="23" t="n">
         <v>0</v>
@@ -2509,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>436388.5000000001</v>
+        <v>437430</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0</v>
@@ -2531,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>362195.4</v>
+        <v>360740.8</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>0</v>
@@ -2595,7 +2593,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>817940.5</v>
+        <v>816240</v>
       </c>
       <c r="H12" s="18" t="n">
         <v>0</v>
@@ -2764,7 +2762,7 @@
         </is>
       </c>
       <c r="B2" s="20" t="n">
-        <v>14493416.45</v>
+        <v>14541450.55</v>
       </c>
       <c r="C2" s="20" t="inlineStr">
         <is>
@@ -2963,16 +2961,16 @@
         </is>
       </c>
       <c r="C2" s="20" t="n">
-        <v>31.8</v>
+        <v>34.1</v>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>NSE live market data</t>
+          <t>NSE live market data unavailable</t>
         </is>
       </c>
       <c r="E2" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2986,7 @@
         </is>
       </c>
       <c r="C3" s="25" t="n">
-        <v>77.5</v>
+        <v>77.25</v>
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
@@ -2997,7 +2995,7 @@
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3020,7 @@
       </c>
       <c r="E4" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3036,7 @@
         </is>
       </c>
       <c r="C5" s="25" t="n">
-        <v>88.75</v>
+        <v>88</v>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
@@ -3047,7 +3045,7 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3061,7 @@
         </is>
       </c>
       <c r="C6" s="20" t="n">
-        <v>31.45</v>
+        <v>31.7</v>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
@@ -3072,7 +3070,7 @@
       </c>
       <c r="E6" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3086,7 @@
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
@@ -3097,7 +3095,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3111,7 @@
         </is>
       </c>
       <c r="C8" s="20" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
@@ -3122,7 +3120,7 @@
       </c>
       <c r="E8" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3136,7 @@
         </is>
       </c>
       <c r="C9" s="25" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
@@ -3147,7 +3145,7 @@
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3170,7 @@
       </c>
       <c r="E10" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3195,7 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3213,7 +3211,7 @@
         </is>
       </c>
       <c r="C12" s="20" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
@@ -3222,7 +3220,7 @@
       </c>
       <c r="E12" s="18" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:19</t>
+          <t>2026-06-05 10:43:00</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3391,7 @@
     <row r="2">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B2" s="17" t="inlineStr">
@@ -3425,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="20" t="n">
-        <v>-4772.700000000012</v>
+        <v>31818</v>
       </c>
       <c r="K2" s="20" t="n">
         <v>510678.9</v>
@@ -3440,7 +3438,7 @@
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B3" s="22" t="inlineStr">
@@ -3472,7 +3470,7 @@
         <v>0</v>
       </c>
       <c r="J3" s="25" t="n">
-        <v>25132.25</v>
+        <v>23199</v>
       </c>
       <c r="K3" s="25" t="n">
         <v>574175.25</v>
@@ -3487,7 +3485,7 @@
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B4" s="17" t="inlineStr">
@@ -3534,7 +3532,7 @@
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B5" s="22" t="inlineStr">
@@ -3566,7 +3564,7 @@
         <v>0</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>2479.5</v>
+        <v>1239.75</v>
       </c>
       <c r="K5" s="25" t="n">
         <v>144224.25</v>
@@ -3581,7 +3579,7 @@
     <row r="6">
       <c r="A6" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
@@ -3613,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="J6" s="20" t="n">
-        <v>35895.60000000009</v>
+        <v>45866.60000000009</v>
       </c>
       <c r="K6" s="20" t="n">
         <v>1218456.2</v>
@@ -3628,7 +3626,7 @@
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B7" s="22" t="inlineStr">
@@ -3660,7 +3658,7 @@
         <v>0</v>
       </c>
       <c r="J7" s="25" t="n">
-        <v>83361</v>
+        <v>90120</v>
       </c>
       <c r="K7" s="25" t="n">
         <v>811080</v>
@@ -3675,7 +3673,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B8" s="17" t="inlineStr">
@@ -3707,7 +3705,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="20" t="n">
-        <v>0</v>
+        <v>1041.499999999942</v>
       </c>
       <c r="K8" s="20" t="n">
         <v>436388.5000000001</v>
@@ -3722,7 +3720,7 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B9" s="22" t="inlineStr">
@@ -3754,7 +3752,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="25" t="n">
-        <v>-11636.80000000005</v>
+        <v>-13091.40000000002</v>
       </c>
       <c r="K9" s="25" t="n">
         <v>373832.2</v>
@@ -3769,7 +3767,7 @@
     <row r="10">
       <c r="A10" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B10" s="17" t="inlineStr">
@@ -3816,7 +3814,7 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B11" s="22" t="inlineStr">
@@ -3863,7 +3861,7 @@
     <row r="12">
       <c r="A12" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B12" s="17" t="inlineStr">
@@ -3895,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>-125837</v>
+        <v>-127537.5</v>
       </c>
       <c r="K12" s="20" t="n">
         <v>943777.5</v>
@@ -3910,7 +3908,7 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B13" s="22" t="inlineStr">
@@ -3957,7 +3955,7 @@
     <row r="14">
       <c r="A14" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B14" s="17" t="inlineStr">
@@ -4004,7 +4002,7 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B15" s="22" t="inlineStr">
@@ -4051,7 +4049,7 @@
     <row r="16">
       <c r="A16" s="17" t="inlineStr">
         <is>
-          <t>2026-06-05 02:02:37</t>
+          <t>2026-06-05 10:43:27</t>
         </is>
       </c>
       <c r="B16" s="17" t="inlineStr">
@@ -4159,10 +4157,10 @@
         <v>32.1</v>
       </c>
       <c r="E2" t="n">
-        <v>31.8</v>
+        <v>34.1</v>
       </c>
       <c r="F2" t="n">
-        <v>505906.2</v>
+        <v>542496.9</v>
       </c>
     </row>
     <row r="3">
@@ -4183,10 +4181,10 @@
         <v>74.25</v>
       </c>
       <c r="E3" t="n">
-        <v>77.5</v>
+        <v>77.25</v>
       </c>
       <c r="F3" t="n">
-        <v>599307.5</v>
+        <v>597374.25</v>
       </c>
     </row>
     <row r="4">
@@ -4231,10 +4229,10 @@
         <v>87.25</v>
       </c>
       <c r="E5" t="n">
-        <v>88.75</v>
+        <v>88</v>
       </c>
       <c r="F5" t="n">
-        <v>146703.75</v>
+        <v>145464</v>
       </c>
     </row>
     <row r="6">
@@ -4255,10 +4253,10 @@
         <v>30.55</v>
       </c>
       <c r="E6" t="n">
-        <v>31.45</v>
+        <v>31.7</v>
       </c>
       <c r="F6" t="n">
-        <v>1254351.8</v>
+        <v>1264322.8</v>
       </c>
     </row>
     <row r="7">
@@ -4279,10 +4277,10 @@
         <v>360</v>
       </c>
       <c r="E7" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>894441</v>
+        <v>901200</v>
       </c>
     </row>
     <row r="8">
@@ -4303,10 +4301,10 @@
         <v>4.19</v>
       </c>
       <c r="E8" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="F8" t="n">
-        <v>436388.5000000001</v>
+        <v>437430</v>
       </c>
     </row>
     <row r="9">
@@ -4327,10 +4325,10 @@
         <v>12.85</v>
       </c>
       <c r="E9" t="n">
-        <v>12.45</v>
+        <v>12.4</v>
       </c>
       <c r="F9" t="n">
-        <v>362195.4</v>
+        <v>360740.8</v>
       </c>
     </row>
     <row r="10">
@@ -4399,10 +4397,10 @@
         <v>55.5</v>
       </c>
       <c r="E12" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>817940.5</v>
+        <v>816240</v>
       </c>
     </row>
     <row r="13">
